--- a/data/ListOfAllParameters.xlsx
+++ b/data/ListOfAllParameters.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="1"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
   </bookViews>
   <sheets>
     <sheet name="Information" sheetId="1" state="visible" r:id="rId2"/>
@@ -181,24 +181,28 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -301,9 +305,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>28</xdr:col>
-      <xdr:colOff>603360</xdr:colOff>
+      <xdr:colOff>603000</xdr:colOff>
       <xdr:row>57</xdr:row>
-      <xdr:rowOff>123480</xdr:rowOff>
+      <xdr:rowOff>123120</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -317,7 +321,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="0" y="2874600"/>
-          <a:ext cx="17725680" cy="8505360"/>
+          <a:ext cx="17725320" cy="8505000"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -350,7 +354,7 @@
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="0" t="s">
+      <c r="A3" s="2" t="s">
         <v>1</v>
       </c>
     </row>
@@ -362,12 +366,12 @@
     <row r="9" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="10" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="12" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="2" t="s">
+      <c r="A12" s="3" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="0" t="str">
+      <c r="A13" s="2" t="str">
         <f aca="false">HYPERLINK("../datatemplates/ProcessDatasheetTemplate.xlsx", "Process datasheet template")</f>
         <v>Process datasheet template</v>
       </c>
@@ -392,52 +396,52 @@
   <dimension ref="A1:G2"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="1" style="0" width="15"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="1" style="2" width="15"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="3" t="s">
+      <c r="A1" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="B1" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="C1" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="D1" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="E1" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="F1" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="G1" s="3" t="s">
+      <c r="G1" s="4" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="4" t="s">
+      <c r="A2" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="B2" s="4" t="s">
+      <c r="B2" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="C2" s="4" t="s">
+      <c r="C2" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="D2" s="4" t="s">
+      <c r="D2" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="E2" s="4" t="s">
+      <c r="E2" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="F2" s="4" t="s">
+      <c r="F2" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="G2" s="4" t="e">
+      <c r="G2" s="5" t="e">
         <f aca="false">HYPERLINK("../data/process/$B2.xlsx";"datasheet")</f>
         <v>#VALUE!</v>
       </c>
